--- a/New_FacetMeanStress/Data_Files/SlideSlideNoTether/4NP_SlideSlide_NoTether_CMS.xlsx
+++ b/New_FacetMeanStress/Data_Files/SlideSlideNoTether/4NP_SlideSlide_NoTether_CMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sjturner.FORTLEWIS\OneDrive - Fort Lewis College\Disc\FCMS results\SlideSlideNoTether\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brburrough\Repo_Git\Spinal-Disc-Replacement-Code\New_FacetMeanStress\Data_Files\SlideSlideNoTether\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{E1AF5369-56CE-4110-9869-C35804E6FFC8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{0182D136-59E8-4C7D-A517-6F471D3445A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9F4EF8-267C-44E3-AD52-F02D44419D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3204" yWindow="3204" windowWidth="17280" windowHeight="9036" xr2:uid="{A3F948EB-09F8-4C60-B1CF-6EBC5CF0D0B5}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{A3F948EB-09F8-4C60-B1CF-6EBC5CF0D0B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="22">
   <si>
     <t>facet stress = facet contact force magnitude/facet contact area</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>5LR_6UR</t>
-  </si>
-  <si>
-    <t>5LL_6UR</t>
   </si>
   <si>
     <t>4LR_5UR</t>
@@ -545,9 +542,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -585,7 +582,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -691,7 +688,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -833,7 +830,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -842,23 +839,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CADCB7FD-BBB6-40E1-BA65-8A94F8027B58}">
   <dimension ref="A1:AN60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="17" max="17" width="9.6640625" customWidth="1"/>
-    <col min="20" max="20" width="9.21875" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -867,7 +864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -878,144 +875,144 @@
         <v>5</v>
       </c>
       <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U5" t="s">
         <v>6</v>
       </c>
-      <c r="U5" t="s">
+      <c r="Z5" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AE5" t="s">
         <v>8</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AJ5" t="s">
         <v>9</v>
       </c>
-      <c r="AJ5" t="s">
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>11</v>
+      </c>
+      <c r="R6" t="s">
+        <v>12</v>
+      </c>
+      <c r="S6" t="s">
+        <v>13</v>
+      </c>
+      <c r="T6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U6" t="s">
+        <v>10</v>
+      </c>
+      <c r="V6" t="s">
+        <v>11</v>
+      </c>
+      <c r="W6" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>12</v>
-      </c>
-      <c r="R6" t="s">
-        <v>13</v>
-      </c>
-      <c r="S6" t="s">
-        <v>14</v>
-      </c>
-      <c r="T6" t="s">
-        <v>15</v>
-      </c>
-      <c r="U6" t="s">
-        <v>11</v>
-      </c>
-      <c r="V6" t="s">
-        <v>12</v>
-      </c>
-      <c r="W6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1153,7 +1150,7 @@
         <v>0.22498990316655929</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2.0512600000000001</v>
       </c>
@@ -1291,7 +1288,7 @@
         <v>0.21305155602419698</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2.1153300000000002</v>
       </c>
@@ -1429,7 +1426,7 @@
         <v>0.19549252429185701</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2.16533</v>
       </c>
@@ -1567,7 +1564,7 @@
         <v>0.18269022555131645</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2.2246999999999999</v>
       </c>
@@ -1705,7 +1702,7 @@
         <v>0.17014788147988943</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2.2668900000000001</v>
       </c>
@@ -1843,7 +1840,7 @@
         <v>0.16137016975100721</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2.3262700000000001</v>
       </c>
@@ -1981,7 +1978,7 @@
         <v>0.15239514912520338</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2.3684599999999998</v>
       </c>
@@ -2119,7 +2116,7 @@
         <v>0.14432979904887563</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2.4278300000000002</v>
       </c>
@@ -2257,7 +2254,7 @@
         <v>0.1354977829215902</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2.4542000000000002</v>
       </c>
@@ -2395,7 +2392,7 @@
         <v>0.12897389075306936</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2.5061499999999999</v>
       </c>
@@ -2533,7 +2530,7 @@
         <v>0.11961583998970872</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2.5507599999999999</v>
       </c>
@@ -2671,7 +2668,7 @@
         <v>0.11309183633327016</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2.60453</v>
       </c>
@@ -2809,7 +2806,7 @@
         <v>0.10800202809508187</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2.65273</v>
       </c>
@@ -2947,7 +2944,7 @@
         <v>9.999474573538808E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2.7006199999999998</v>
       </c>
@@ -3085,7 +3082,7 @@
         <v>9.2839695112838141E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2.75176</v>
       </c>
@@ -3223,7 +3220,7 @@
         <v>8.6909477576552971E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2.80444</v>
       </c>
@@ -3361,7 +3358,7 @@
         <v>7.9901949024048513E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2.8583699999999999</v>
       </c>
@@ -3499,7 +3496,7 @@
         <v>7.5921698963902898E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2.9134199999999999</v>
       </c>
@@ -3637,7 +3634,7 @@
         <v>6.929815171411767E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2.9619599999999999</v>
       </c>
@@ -3775,7 +3772,7 @@
         <v>6.2668578762480331E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3913,17 +3910,17 @@
         <v>5.8830356722740278E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>1</v>
@@ -3932,12 +3929,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -3948,144 +3945,144 @@
         <v>5</v>
       </c>
       <c r="P34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U34" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z34" t="s">
         <v>7</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AE34" t="s">
         <v>8</v>
       </c>
-      <c r="AE34" t="s">
+      <c r="AJ34" t="s">
         <v>9</v>
       </c>
-      <c r="AJ34" t="s">
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>10</v>
       </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" t="s">
+        <v>11</v>
+      </c>
+      <c r="M35" t="s">
+        <v>12</v>
+      </c>
+      <c r="N35" t="s">
+        <v>13</v>
+      </c>
+      <c r="O35" t="s">
+        <v>14</v>
+      </c>
+      <c r="P35" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>11</v>
+      </c>
+      <c r="R35" t="s">
+        <v>12</v>
+      </c>
+      <c r="S35" t="s">
+        <v>13</v>
+      </c>
+      <c r="T35" t="s">
+        <v>14</v>
+      </c>
+      <c r="U35" t="s">
+        <v>10</v>
+      </c>
+      <c r="V35" t="s">
+        <v>11</v>
+      </c>
+      <c r="W35" t="s">
+        <v>12</v>
+      </c>
+      <c r="X35" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K35" t="s">
-        <v>11</v>
-      </c>
-      <c r="L35" t="s">
-        <v>12</v>
-      </c>
-      <c r="M35" t="s">
-        <v>13</v>
-      </c>
-      <c r="N35" t="s">
-        <v>14</v>
-      </c>
-      <c r="O35" t="s">
-        <v>15</v>
-      </c>
-      <c r="P35" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>12</v>
-      </c>
-      <c r="R35" t="s">
-        <v>13</v>
-      </c>
-      <c r="S35" t="s">
-        <v>14</v>
-      </c>
-      <c r="T35" t="s">
-        <v>15</v>
-      </c>
-      <c r="U35" t="s">
-        <v>11</v>
-      </c>
-      <c r="V35" t="s">
-        <v>12</v>
-      </c>
-      <c r="W35" t="s">
-        <v>13</v>
-      </c>
-      <c r="X35" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2</v>
       </c>
@@ -4223,7 +4220,7 @@
         <v>0.22498990316655929</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2.0512600000000001</v>
       </c>
@@ -4361,7 +4358,7 @@
         <v>0.24776157138471355</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2.1153300000000002</v>
       </c>
@@ -4499,7 +4496,7 @@
         <v>0.27836506367193109</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2.1747100000000001</v>
       </c>
@@ -4637,7 +4634,7 @@
         <v>0.32720343655520484</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2.20404</v>
       </c>
@@ -4775,7 +4772,7 @@
         <v>0.3554789920660848</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2.2512099999999999</v>
       </c>
@@ -4913,7 +4910,7 @@
         <v>0.4006311608241645</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2.3028900000000001</v>
       </c>
@@ -5051,7 +5048,7 @@
         <v>0.44393309998396185</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2.3528600000000002</v>
       </c>
@@ -5189,7 +5186,7 @@
         <v>0.49483515970859843</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2.4111699999999998</v>
       </c>
@@ -5327,7 +5324,7 @@
         <v>0.5420736556743726</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2.4602499999999998</v>
       </c>
@@ -5465,7 +5462,7 @@
         <v>0.58289980714161949</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2.51267</v>
       </c>
@@ -5603,7 +5600,7 @@
         <v>0.63109185832509107</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2.5564</v>
       </c>
@@ -5741,7 +5738,7 @@
         <v>0.67490477589380093</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2.6033400000000002</v>
       </c>
@@ -5879,7 +5876,7 @@
         <v>0.73257845075761463</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2.6604800000000002</v>
       </c>
@@ -6017,7 +6014,7 @@
         <v>0.78589169498821099</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2.7082199999999998</v>
       </c>
@@ -6155,7 +6152,7 @@
         <v>0.83563151078617015</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2.7589999999999999</v>
       </c>
@@ -6293,7 +6290,7 @@
         <v>0.89019504767429225</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2.8092299999999999</v>
       </c>
@@ -6431,7 +6428,7 @@
         <v>0.94053478798715129</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2.8506100000000001</v>
       </c>
@@ -6569,7 +6566,7 @@
         <v>0.99341418024801798</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2.90524</v>
       </c>
@@ -6707,7 +6704,7 @@
         <v>1.0528032545056394</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2.9500299999999999</v>
       </c>
@@ -6845,7 +6842,7 @@
         <v>1.1045825347876723</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>3</v>
       </c>
@@ -6983,7 +6980,7 @@
         <v>1.1615434933430242</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="E60" s="1"/>
       <c r="J60" s="1"/>
     </row>
@@ -7228,18 +7225,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7262,18 +7259,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01A14A9E-50E2-40B0-9FB8-D27D13AAEB0E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E16A3AC-0D1E-4991-8831-1D4F4924E3DF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01A14A9E-50E2-40B0-9FB8-D27D13AAEB0E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>